--- a/presentation/grading_sheet_h23vilmu.xlsx
+++ b/presentation/grading_sheet_h23vilmu.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dalarnauniversity-my.sharepoint.com/personal/h23vilmu_du_se/Documents/[6] GDT3CR Etisk Hackning/Project Work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ViliM\Documents\GitHub\PromptInjectionCTF\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_38C9E9258E3ADB3DAE2DA05967DBC9CD9150D37D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AF01C24-6EBE-4BE3-BCB2-F489E2A21434}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C2F973-32C7-4F37-9CEB-B41D04F9464D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3195" yWindow="1815" windowWidth="21600" windowHeight="12645" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -293,9 +293,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>Your name:Vili Mujkanovic</t>
-  </si>
-  <si>
     <t>Mattias Arvidsson</t>
   </si>
   <si>
@@ -321,6 +318,9 @@
   </si>
   <si>
     <t>bra att ha testat under demo med eget skapat virus.</t>
+  </si>
+  <si>
+    <t>Your name: Vili Mujkanovic</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J3"/>
     </row>
@@ -673,10 +673,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -685,13 +685,13 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J14"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="6">
         <v>4</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="16" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="6">
         <v>4</v>
@@ -719,13 +719,13 @@
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
       <c r="I16" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6">
         <v>4</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6">
         <v>4</v>
@@ -753,7 +753,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J18"/>
     </row>
